--- a/Encollect_Web_DBS_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
+++ b/Encollect_Web_DBS_P3/Cypress/fixtures/ProductMasterTemplate.xlsx
@@ -32,8 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="d\ mmm\ yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +67,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,113 +404,113 @@
   <dimension ref="A1:C11"/>
   <sheetData>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Shoes</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Bespoke Steel Salad</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Small</v>
+      <c r="A2" s="1" t="str">
+        <v>Beauty</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v>Refined Plastic Soap</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>Oriental</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Music</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Practical Wooden Car</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="A3" s="1" t="str">
+        <v>Books</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>Soft Marble Chicken</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>Bespoke</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="str">
+        <v>Toys</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <v>Generic Wooden Towels</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>Handcrafted</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="str">
+        <v>Jewelry</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <v>Soft Silk Salad</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <v>Licensed</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="str">
+        <v>Tools</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v>Luxurious Bronze Salad</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>Incredible</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="str">
+        <v>Computers</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <v>Soft Gold Ball</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <v>Luxurious</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v>Unbranded Wooden Shoes</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <v>Oriental</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="str">
+        <v>Books</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v>Small Bronze Gloves</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <v>Electronic</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>Health</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v>Ergonomic Silk Chips</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <v>Luxurious</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="str">
+        <v>Industrial</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <v>Luxurious Marble Sausages</v>
+      </c>
+      <c r="C11" s="1" t="str">
         <v>Practical</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Baby</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Generic Steel Car</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Intelligent</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Baby</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Awesome Granite Mouse</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Small</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Garden</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Recycled Plastic Pizza</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Refined</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Grocery</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Handmade Fresh Chair</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Awesome</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Tools</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Elegant Wooden Table</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Refined</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Automotive</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Practical Frozen Bike</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Handcrafted</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Automotive</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Handmade Concrete Bike</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Intelligent</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Jewelry</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Awesome Soft Table</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Refined</v>
       </c>
     </row>
   </sheetData>
